--- a/demo_send/formwork_ITP-1052_2026-08.xlsx
+++ b/demo_send/formwork_ITP-1052_2026-08.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formwork report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Formwork report" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -523,6 +523,66 @@
         <v>317951</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Tidel Park Block C - Taramani</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Slab formwork</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>159000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Tidel Park Block C - Taramani</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Column and beam formwork</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>95400</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Tidel Park Block C - Taramani</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Staircase and miscellaneous formwork</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>63551</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
